--- a/public/post/drafts/season-prediction/men_model-resursive-tests-actual_mae.xlsx
+++ b/public/post/drafts/season-prediction/men_model-resursive-tests-actual_mae.xlsx
@@ -509,25 +509,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0883334518503782</v>
+        <v>0.0906383451806958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.124123763322625</v>
+        <v>0.123718518580357</v>
       </c>
       <c r="D5" t="n">
-        <v>0.170778028667348</v>
+        <v>0.170055747781389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.118591668141314</v>
+        <v>0.118397507593497</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0994421060770735</v>
+        <v>0.102380897703714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.118937282933757</v>
+        <v>0.118230893320764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.120034383498749</v>
+        <v>0.120570318360069</v>
       </c>
     </row>
     <row r="6">
